--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,29 +8489,29 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>511</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>643</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>334</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
@@ -8640,11 +8640,11 @@
         <v>69</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8680,14 +8680,14 @@
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8714,28 +8714,28 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>225</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>234</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
         <v>274</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -8795,17 +8795,17 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9027,11 +9027,11 @@
         <v>37</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>132</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
@@ -9156,16 +9156,16 @@
         <v>5</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>12/09/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9199,11 +9199,11 @@
         <v>2</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9285,11 +9285,11 @@
         <v>33</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9311,17 +9311,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="F21" s="10" t="n">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9586,11 +9586,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>07/2026</t>
+          <t>08/2026</t>
         </is>
       </c>
     </row>
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9827,28 +9827,28 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>13/09/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,29 +8489,29 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>1,070</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" s="10" t="n">
         <v>1</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>28</v>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
@@ -8597,11 +8597,11 @@
         <v>85</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8683,11 +8683,11 @@
         <v>12</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8726,11 +8726,11 @@
         <v>274</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="F8" s="10" t="n">
@@ -8855,11 +8855,11 @@
         <v>5</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F12" s="10" t="n">
@@ -9027,11 +9027,11 @@
         <v>37</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9113,11 +9113,11 @@
         <v>17</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9156,11 +9156,11 @@
         <v>5</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>12/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9268,17 +9268,17 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="F20" s="10" t="n">
@@ -9328,11 +9328,11 @@
         <v>17</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9497,14 +9497,14 @@
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>19/09/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9586,11 +9586,11 @@
         <v>33</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9844,11 +9844,11 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>13/09/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>1,070</t>
+          <t>511</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -8551,14 +8551,14 @@
         </is>
       </c>
       <c r="F3" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>29/08/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -8585,23 +8585,23 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>412</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>335</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8637,14 +8637,14 @@
         </is>
       </c>
       <c r="F5" s="10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>78</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8680,14 +8680,14 @@
         </is>
       </c>
       <c r="F6" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="10" t="n">
         <v>51</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8723,14 +8723,14 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -8766,19 +8766,19 @@
         </is>
       </c>
       <c r="F8" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G8" s="10" t="n">
         <v>40</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -8809,14 +8809,14 @@
         </is>
       </c>
       <c r="F9" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>26/09/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8852,14 +8852,14 @@
         </is>
       </c>
       <c r="F10" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>16</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8895,14 +8895,14 @@
         </is>
       </c>
       <c r="F11" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>119</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8938,14 +8938,14 @@
         </is>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>14</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>14/02/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8981,14 +8981,14 @@
         </is>
       </c>
       <c r="F13" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>28</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9024,14 +9024,14 @@
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9067,14 +9067,14 @@
         </is>
       </c>
       <c r="F15" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>7</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9110,14 +9110,14 @@
         </is>
       </c>
       <c r="F16" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>37</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9153,14 +9153,14 @@
         </is>
       </c>
       <c r="F17" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -9196,14 +9196,14 @@
         </is>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9239,14 +9239,14 @@
         </is>
       </c>
       <c r="F19" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" s="10" t="n">
         <v>70</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>18/07/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9282,14 +9282,14 @@
         </is>
       </c>
       <c r="F20" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9316,23 +9316,23 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="F21" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G21" s="10" t="n">
         <v>15</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9368,14 +9368,14 @@
         </is>
       </c>
       <c r="F22" s="10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G22" s="10" t="n">
         <v>5</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9411,14 +9411,14 @@
         </is>
       </c>
       <c r="F23" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="10" t="n">
         <v>137</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9497,14 +9497,14 @@
         </is>
       </c>
       <c r="F25" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>19/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9540,14 +9540,14 @@
         </is>
       </c>
       <c r="F26" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" s="10" t="n">
         <v>27</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -9583,14 +9583,14 @@
         </is>
       </c>
       <c r="F27" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G27" s="10" t="n">
         <v>89</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9626,14 +9626,14 @@
         </is>
       </c>
       <c r="F28" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G28" s="10" t="n">
         <v>4</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9669,14 +9669,14 @@
         </is>
       </c>
       <c r="F29" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="10" t="n">
         <v>9</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
-          <t>14/02/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>15/09/2026</t>
+          <t>25/09/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>15/08/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9841,14 +9841,14 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
         <v>22</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,22 +8489,22 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>1,070</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -8580,33 +8580,33 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>413</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
         <v>86</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -8723,14 +8723,14 @@
         </is>
       </c>
       <c r="F7" s="10" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>13</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9096,28 +9096,28 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>205</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>134</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
         <v>18</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9294,7 +9294,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F22" s="10" t="n">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9500,16 +9500,16 @@
         <v>45</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8563,7 +8563,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -8580,28 +8580,28 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>418</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>336</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
         <v>86</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>158</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -8726,11 +8726,11 @@
         <v>276</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9027,11 +9027,11 @@
         <v>38</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9156,16 +9156,16 @@
         <v>6</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9199,11 +9199,11 @@
         <v>3</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>06/10/2026</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9371,11 +9371,11 @@
         <v>56</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9586,11 +9586,11 @@
         <v>34</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>08/2026</t>
+          <t>09/2026</t>
         </is>
       </c>
     </row>
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>25/09/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F31" s="15" t="n">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8489,33 +8489,33 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>1,070</t>
+          <t>511</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F2" s="10" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -8580,28 +8580,28 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>651</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>420</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>338</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
         <v>86</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8628,23 +8628,23 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>95</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
         <v>70</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>17/10/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9024,14 +9024,14 @@
         </is>
       </c>
       <c r="F14" s="10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G14" s="10" t="n">
         <v>78</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9113,11 +9113,11 @@
         <v>18</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9586,11 +9586,11 @@
         <v>34</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>05/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9715,11 +9715,11 @@
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>16/10/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9827,17 +9827,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F33" t="n">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8508,14 +8508,14 @@
         </is>
       </c>
       <c r="F2" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="10" t="n">
-        <v>28</v>
-      </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -8580,17 +8580,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>655</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>426</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>342</t>
         </is>
       </c>
       <c r="F4" s="10" t="n">
@@ -8640,11 +8640,11 @@
         <v>70</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>17/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8726,11 +8726,11 @@
         <v>276</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8812,11 +8812,11 @@
         <v>9</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>26/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9015,23 +9015,23 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F14" s="10" t="n">
         <v>39</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F15" s="10" t="n">
@@ -9328,16 +9328,16 @@
         <v>18</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>21/10/2026</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
@@ -9371,11 +9371,11 @@
         <v>56</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>20/10/2026</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9698,28 +9698,28 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>357</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>261</t>
         </is>
       </c>
       <c r="F30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>16/10/2026</t>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>09/2026</t>
+          <t>10/2026</t>
         </is>
       </c>
     </row>
